--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CF6D2D-4389-4337-B94E-8D96223F1AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C007A131-6651-4D6D-AB87-1B9BEDB41AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 19-12-2025'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 29-01-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C007A131-6651-4D6D-AB87-1B9BEDB41AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11C8E7C-1559-486E-857A-53592D6B435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 29-01-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 02-02-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11C8E7C-1559-486E-857A-53592D6B435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37E5199-62C1-4A18-BCC5-0D539E3E18FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 02-02-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 20-02-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -765,7 +765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37E5199-62C1-4A18-BCC5-0D539E3E18FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA65106-C865-4D5A-9F73-8B3521D54A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 20-02-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 04-03-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA65106-C865-4D5A-9F73-8B3521D54A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DF4079-3144-451A-938E-153B9E6FB663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 04-03-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 06-03-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DF4079-3144-451A-938E-153B9E6FB663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7C3A40-8C04-4378-A3EB-A8388DF9E566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7C3A40-8C04-4378-A3EB-A8388DF9E566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0647AE43-867D-4688-A674-217BD469FE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0647AE43-867D-4688-A674-217BD469FE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21EAC77-FAD0-4630-9406-59CF71E4C653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 06-03-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 09-03-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21EAC77-FAD0-4630-9406-59CF71E4C653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC76D86C-3F78-40E7-9520-69112740BC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC76D86C-3F78-40E7-9520-69112740BC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112D9327-3A1E-477D-8B4B-BBA063A1ADA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 09-03-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 11-03-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112D9327-3A1E-477D-8B4B-BBA063A1ADA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB65758-F3E9-478F-A80C-91E95B86AEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB65758-F3E9-478F-A80C-91E95B86AEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C804535A-85A9-4A20-A0A5-0CF7BD564065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 11-03-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 20-03-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C804535A-85A9-4A20-A0A5-0CF7BD564065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841CD7C1-A964-47B9-8D55-35F8A85376B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 20-03-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 25-03-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841CD7C1-A964-47B9-8D55-35F8A85376B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1190038-F5EE-4E34-A21E-8A3DDEA6DA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 25-03-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 08-04-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1190038-F5EE-4E34-A21E-8A3DDEA6DA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96ED1FC0-A264-4248-95F7-CCCF2908F78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 08-04-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 10-04-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96ED1FC0-A264-4248-95F7-CCCF2908F78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50685E09-EA8B-48B1-A02D-D7F5B974E385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50685E09-EA8B-48B1-A02D-D7F5B974E385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E995438E-1DC1-417D-B264-C37DDAD58FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 10-04-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 14-04-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E995438E-1DC1-417D-B264-C37DDAD58FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5EA485-C29D-466C-871D-9CF737EBACBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 14-04-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 24-04-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5EA485-C29D-466C-871D-9CF737EBACBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C77E83C-546E-4861-BB65-09DB80D1096D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
     <t>Sensum Bosted _EOJ_ (EG)</t>
   </si>
   <si>
-    <t>VITAE Suite (Dedalus)</t>
+    <t>VITAE Suite (Dedalus Healthcare Denmark)</t>
   </si>
   <si>
     <t>Acknowledgement</t>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C77E83C-546E-4861-BB65-09DB80D1096D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBCDA80-A821-4CA8-B4D0-75C3DF291BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 24-04-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 27-04-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -76,7 +76,7 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (4.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Care Plan</t>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBCDA80-A821-4CA8-B4D0-75C3DF291BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B61EB2F-854F-4CA1-98FE-4BB041A3C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 27-04-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 06-05-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B61EB2F-854F-4CA1-98FE-4BB041A3C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F998613-E8E6-4365-8570-52DBD7E5F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 06-05-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 01-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F998613-E8E6-4365-8570-52DBD7E5F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A3F713-3645-4576-8C6A-78C8530B2C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 01-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 02-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A3F713-3645-4576-8C6A-78C8530B2C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44336814-ED42-40A8-903F-45F14A8285BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44336814-ED42-40A8-903F-45F14A8285BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A579C71D-4345-41CC-A881-116B4AB97CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 02-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 05-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C007A131-6651-4D6D-AB87-1B9BEDB41AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8A5DFB-15B3-4248-A48C-C95F99797B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8A5DFB-15B3-4248-A48C-C95F99797B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C492B505-60C9-456D-B374-0D40BA9F7C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 29-01-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 09-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -49,7 +49,7 @@
     <t>Sensum Bosted _EOJ_ (EG)</t>
   </si>
   <si>
-    <t>VITAE Suite (Dedalus)</t>
+    <t>VITAE Suite (Dedalus Healthcare Denmark)</t>
   </si>
   <si>
     <t>Acknowledgement</t>
@@ -76,7 +76,7 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (4.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Care Plan</t>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C492B505-60C9-456D-B374-0D40BA9F7C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECC94F8-2B14-47D1-989B-AFAD5AB293A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECC94F8-2B14-47D1-989B-AFAD5AB293A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66483BD-66C3-4A21-8049-44A844CB078C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66483BD-66C3-4A21-8049-44A844CB078C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A676E9-A1F9-470D-B03A-B01588ED4979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 09-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 15-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -765,7 +765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A676E9-A1F9-470D-B03A-B01588ED4979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1A04D0-1612-4C7F-A4D9-A9096671CB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 15-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 22-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1A04D0-1612-4C7F-A4D9-A9096671CB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCE6744-E544-4B34-B7C4-756127BBD17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 22-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 23-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -765,7 +765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCE6744-E544-4B34-B7C4-756127BBD17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D757D6-DEF6-4C2A-AE20-5F03F0A891C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1A04D0-1612-4C7F-A4D9-A9096671CB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3003AFE-2ECF-46A4-A822-F8AA885F2750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 22-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 23-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3003AFE-2ECF-46A4-A822-F8AA885F2750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8E4A2E-1597-46CA-B64F-B9FF936BBE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 23-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 25-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8E4A2E-1597-46CA-B64F-B9FF936BBE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747A4386-21D4-4C60-833B-06955067AB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 25-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 30-06-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747A4386-21D4-4C60-833B-06955067AB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A860B51E-DCDD-4386-987E-DFC4A5A4838D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A860B51E-DCDD-4386-987E-DFC4A5A4838D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281904BA-52A9-439C-9E67-7B5248704541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 30-06-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 01-07-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -61,6 +61,9 @@
     <t>Modtage</t>
   </si>
   <si>
+    <t>Godkendt</t>
+  </si>
+  <si>
     <t>Tester</t>
   </si>
   <si>
@@ -68,9 +71,6 @@
   </si>
   <si>
     <t>APD-DK (2.0.1)</t>
-  </si>
-  <si>
-    <t>Godkendt</t>
   </si>
   <si>
     <t>CareCommunication</t>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -722,30 +722,30 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -759,13 +759,13 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -776,13 +776,13 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -793,10 +793,10 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -807,10 +807,10 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -821,10 +821,10 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -835,13 +835,13 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -852,10 +852,10 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -866,10 +866,10 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,13 +880,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -897,16 +897,16 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -917,19 +917,19 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -940,16 +940,16 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -960,13 +960,13 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -977,10 +977,10 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -991,13 +991,13 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1008,16 +1008,16 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1028,10 +1028,10 @@
         <v>11</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1042,22 +1042,22 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1068,22 +1068,22 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1094,22 +1094,22 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1120,13 +1120,13 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1137,10 +1137,10 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1151,25 +1151,25 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1180,13 +1180,13 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1197,19 +1197,19 @@
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1220,13 +1220,13 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1237,13 +1237,13 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1254,19 +1254,19 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1277,22 +1277,22 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1303,13 +1303,13 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1320,19 +1320,19 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H34" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1343,10 +1343,10 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1357,22 +1357,22 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1383,13 +1383,13 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1400,10 +1400,10 @@
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1414,13 +1414,13 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1431,19 +1431,19 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H40" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1454,19 +1454,19 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1477,16 +1477,16 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1497,36 +1497,36 @@
         <v>86</v>
       </c>
       <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
         <v>15</v>
       </c>
-      <c r="E43" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>13</v>
-      </c>
-      <c r="B44" t="s">
-        <v>14</v>
-      </c>
       <c r="C44" t="s">
         <v>86</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -1540,13 +1540,13 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1557,10 +1557,10 @@
         <v>86</v>
       </c>
       <c r="E46" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1571,10 +1571,10 @@
         <v>86</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1585,10 +1585,10 @@
         <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1599,16 +1599,16 @@
         <v>86</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H49" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1619,13 +1619,13 @@
         <v>86</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1636,13 +1636,13 @@
         <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1653,16 +1653,16 @@
         <v>86</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1673,10 +1673,10 @@
         <v>86</v>
       </c>
       <c r="H53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1687,10 +1687,10 @@
         <v>86</v>
       </c>
       <c r="H54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1701,22 +1701,22 @@
         <v>86</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I55" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1727,22 +1727,22 @@
         <v>86</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I56" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1753,16 +1753,16 @@
         <v>86</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I57" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1773,10 +1773,10 @@
         <v>86</v>
       </c>
       <c r="I58" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1787,16 +1787,16 @@
         <v>86</v>
       </c>
       <c r="D59" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I59" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1807,13 +1807,13 @@
         <v>86</v>
       </c>
       <c r="F60" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I60" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1824,19 +1824,19 @@
         <v>86</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H61" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I61" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1847,16 +1847,16 @@
         <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I62" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1867,22 +1867,22 @@
         <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H63" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I63" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1893,16 +1893,16 @@
         <v>86</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I64" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>86</v>
       </c>
       <c r="H65" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281904BA-52A9-439C-9E67-7B5248704541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700F2297-4153-4184-9FA4-2B185BDDC001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 01-07-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 02-07-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281904BA-52A9-439C-9E67-7B5248704541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A15D1A-63CE-4E00-A36B-C0169CE75808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 01-07-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 03-07-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -765,7 +765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700F2297-4153-4184-9FA4-2B185BDDC001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71B8726-4106-491D-87DF-5EAF9C907385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 02-07-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 03-07-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -765,7 +765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71B8726-4106-491D-87DF-5EAF9C907385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0C486E-D639-4633-9AD6-AA409037325D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 03-07-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 09-07-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -64,19 +64,19 @@
     <t>Godkendt</t>
   </si>
   <si>
+    <t>Appointment Document</t>
+  </si>
+  <si>
+    <t>APD-DK (2.0.1)</t>
+  </si>
+  <si>
+    <t>CareCommunication</t>
+  </si>
+  <si>
+    <t>CareCommunication (5.0)</t>
+  </si>
+  <si>
     <t>Tester</t>
-  </si>
-  <si>
-    <t>Appointment Document</t>
-  </si>
-  <si>
-    <t>APD-DK (2.0.1)</t>
-  </si>
-  <si>
-    <t>CareCommunication</t>
-  </si>
-  <si>
-    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Care Plan</t>
@@ -722,15 +722,15 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -747,22 +747,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -963,7 +963,7 @@
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1386,7 +1386,7 @@
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -1500,7 +1500,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
         <v>14</v>
-      </c>
-      <c r="B44" t="s">
-        <v>15</v>
       </c>
       <c r="C44" t="s">
         <v>86</v>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
         <v>16</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
         <v>17</v>
-      </c>
-      <c r="C45" t="s">
-        <v>86</v>
-      </c>
-      <c r="D45" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0C486E-D639-4633-9AD6-AA409037325D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B852DD15-BDC3-4868-B560-32F458BEC573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 09-07-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 19-08-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B852DD15-BDC3-4868-B560-32F458BEC573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF4D809-16EA-4CF3-920A-DC26D035819F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 19-08-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 21-08-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF4D809-16EA-4CF3-920A-DC26D035819F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CE995B-5871-43C2-BCDB-D440570C08CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 21-08-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 27-08-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CE995B-5871-43C2-BCDB-D440570C08CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B4879A-2916-4E2D-AD4F-46CB35BECAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 27-08-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 02-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B4879A-2916-4E2D-AD4F-46CB35BECAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A03AD3-F357-4DBF-86BB-DA4E975E8A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 02-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 06-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A03AD3-F357-4DBF-86BB-DA4E975E8A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFD8D46-52CD-403A-ABCD-C9C33F7F8556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFD8D46-52CD-403A-ABCD-C9C33F7F8556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB1036D-96F9-47F0-BE53-2515FA90DE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 06-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 07-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB1036D-96F9-47F0-BE53-2515FA90DE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7907D51B-0F5D-47F8-B9A9-8F4A18F3E70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 07-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 09-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7907D51B-0F5D-47F8-B9A9-8F4A18F3E70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981ABF7A-6368-4D8A-8B73-E1F1F2F0946F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
